--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC I/LTAIPT_A63F01.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC I/LTAIPT_A63F01.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="7365"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="210">
   <si>
     <t>48946</t>
   </si>
@@ -134,418 +134,463 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2021</t>
+    <t>4276F3FB748C85686F9B96A544BB983C</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>Reglamento</t>
+  </si>
+  <si>
+    <t>Reglamento Interior de la Secretaría de la Función Pública</t>
+  </si>
+  <si>
+    <t>20/02/2012</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/reglamento%20interior%20de%20la%20secretaria%20de%20la%20funcion%20publica%20tlax%20220212.pdf</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>27804D14BC68CA4A19993513F14CDF1F</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>28/04/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/PUBLICACI%c3%93N%20PER.%20OFICIAL%20REGLAMENTO%20INTERIOR%20COBAT.pdf</t>
+  </si>
+  <si>
+    <t>F15C7EDEF90B9DD0E6781C2ED23F9C34</t>
+  </si>
+  <si>
+    <t>Reglamento General de la Ley que Crea al Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>06/02/1985</t>
+  </si>
+  <si>
+    <t>50C9FFD992DF8207B9CCB58E418710C6</t>
   </si>
   <si>
     <t>Código</t>
   </si>
   <si>
-    <t>Código Civil vigente en el Estado de Tlaxcala</t>
+    <t>Código de Ética y Reglas de Integridad para las y los Servidores Públicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>07/07/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/C%C3%93DIGO%20DE%20%C3%89TICA%20Y%20REGLAS%20DE%20INTEGRIDAD%20DE%20COBAT%20PUBLICADO%20EN%20PERI%C3%93DICO%20OFICIAL.pdf</t>
+  </si>
+  <si>
+    <t>870D8F44F6B5E08CF8063DE88C4E31D1</t>
+  </si>
+  <si>
+    <t>Código de Conducta para las y los Servidores Públicos del Organismo Público Desconcentrado del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/CODIGO%20DE%20CONDUCTA%20COBAT.pdf</t>
+  </si>
+  <si>
+    <t>022ED096A0DFA978E9016D9DB41664B3</t>
+  </si>
+  <si>
+    <t>Código Penal vigente en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>02/01/1980</t>
+  </si>
+  <si>
+    <t>13/09/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_penal_TLAX130921.pdf</t>
+  </si>
+  <si>
+    <t>B6E018569790010465B2F846450B99D4</t>
+  </si>
+  <si>
+    <t>Código Nacional de Procedimientos Penales</t>
+  </si>
+  <si>
+    <t>05/03/2014</t>
+  </si>
+  <si>
+    <t>09/02/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CODIGO-NAC-PROCED-PENALES_190221.pdf</t>
+  </si>
+  <si>
+    <t>E96392665A015D0BF6CF2A6315E23918</t>
+  </si>
+  <si>
+    <t>Código Penal Federal</t>
+  </si>
+  <si>
+    <t>14/08/2031</t>
+  </si>
+  <si>
+    <t>12/11/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CODIGO-PENAL-FED121121.pdf</t>
+  </si>
+  <si>
+    <t>2A1C7A7F634CDB6F8EDDC942C249929F</t>
+  </si>
+  <si>
+    <t>Código de Procedimientos Civiles vigente en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/11/1980</t>
+  </si>
+  <si>
+    <t>04/09/2018</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_de_proced_civiles040918.pdf</t>
+  </si>
+  <si>
+    <t>B0ED5BBE161194F880FEE44D77056E7E</t>
+  </si>
+  <si>
+    <t>Código Civil en el Estado de Tlaxcala</t>
   </si>
   <si>
     <t>20/11/1976</t>
   </si>
   <si>
-    <t>30/12/2016</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/C%C3%B3digo-Civil-para-el-Estado-Libre-y-Soberano-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Código de Procedimientos Civiles vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/11/1980</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/C%C3%B3digo-de-Procedimientos-Civiles-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Código Penal Penal Federal</t>
-  </si>
-  <si>
-    <t>14/08/2031</t>
-  </si>
-  <si>
-    <t>24/01/2020</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202020/Subdireccion%20Juridica/1er-Trimestre/Codigo_Penal_Federal_Reforma240120.pdf</t>
-  </si>
-  <si>
-    <t>Código Nacional de Procedimientos Penales</t>
-  </si>
-  <si>
-    <t>05/03/2014</t>
-  </si>
-  <si>
-    <t>22/01/2020</t>
-  </si>
-  <si>
-    <t>Código Penal vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>02/01/1980</t>
-  </si>
-  <si>
-    <t>19/05/2016</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/C%C3%B3digo-Penal-para-el-Estado-Libre-y-Soberano-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Código de Procedimientos Penales vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>18/12/1979</t>
-  </si>
-  <si>
-    <t>24/12/2014</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/C%C3%B3digo-de-Procedimientos-Penales-para-el-Estado-Libre-y-Soberano-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Reglamento</t>
-  </si>
-  <si>
-    <t>Reglamento Interior de la Contraloria del Ejecutivo del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>16/10/2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Reglamento%20Interior%20de%20la%20Contralor%C3%ADa%20del%20Ejecutivo%20del%20Estado%20de%20Tlaxcala%2016oct2019.pdf</t>
-  </si>
-  <si>
-    <t>Al ser un nuevo Reglamento  no existe fecha de modificación o reforma</t>
+    <t>25/04/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_civil_Tlax240422.pdf</t>
+  </si>
+  <si>
+    <t>6E69A1D01BBD958F931B46B6A907DEEB</t>
+  </si>
+  <si>
+    <t>Ley Reglamentaria</t>
+  </si>
+  <si>
+    <t>Ley Reglamentaria del Artículo 3ro de la Constitución Política de los Estados Unidos Mexicanos, en Materia de Mejora Continua de la Educación</t>
+  </si>
+  <si>
+    <t>30/09/2019</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Reglamentaria%20del%20art.%203%20de%20la%20CPM%20en%20materia%20de%20mejora%20continua%20de%20la%20Educacion.pdf</t>
+  </si>
+  <si>
+    <t>74AAE2881415EC5888C252859044B088</t>
+  </si>
+  <si>
+    <t>Ley Local</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>05/08/1981</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_que_crea_el_Colegio_de_Bachilleres_del_Estado_de_Tlaxcala.pdf</t>
+  </si>
+  <si>
+    <t>A29CF1167164FBDE5608941E30E513BB</t>
+  </si>
+  <si>
+    <t>Ley de Mejora Regulatoria del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>09/05/2013</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Mejora_Regulatoria_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
+  </si>
+  <si>
+    <t>4455EC723E0423F0E85A7A7AD9A604B6</t>
+  </si>
+  <si>
+    <t>Ley de Archivos del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/05/2011</t>
+  </si>
+  <si>
+    <t>10/05/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_Archivos_Tlaxcala100521.pdf</t>
+  </si>
+  <si>
+    <t>4C9602F88C6A2A5E164909240FE0519E</t>
+  </si>
+  <si>
+    <t>Ley de Protección de Datos Personales en Posesión de Sujetos Obligados del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>14/05/2012</t>
+  </si>
+  <si>
+    <t>18/07/2017</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/LEY_DE_DATOS.pdf</t>
+  </si>
+  <si>
+    <t>CF4C3986F0C3619D00EFFABB4F963C0D</t>
+  </si>
+  <si>
+    <t>Ley de Entrega- Recepción para el Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>18/05/2011</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Entrega_Recepcion_para_el_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
+  </si>
+  <si>
+    <t>41648A57CE4673410AA305F25AAE9F00</t>
+  </si>
+  <si>
+    <t>Ley de Transparencia y Acceso a la Información Pública del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>22/05/2012</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_transparencia-Tlax_aaceso_inf_pub_tlax1430921.pdf</t>
+  </si>
+  <si>
+    <t>79C6FB3E4CCFF07CAB2B031DDB3BC08A</t>
+  </si>
+  <si>
+    <t>Ley del Procedimiento Administrativo del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>30/11/2001</t>
+  </si>
+  <si>
+    <t>12/04/2018</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_del_procedimiento_Admtvo_Tlax120418.pdf</t>
+  </si>
+  <si>
+    <t>D352CF9920CE5D13C8172D0F3AD7A349</t>
+  </si>
+  <si>
+    <t>Ley Orgánica</t>
+  </si>
+  <si>
+    <t>Ley Orgánica para la Administración Pública del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>07/04/1948</t>
+  </si>
+  <si>
+    <t>02/06/2022</t>
+  </si>
+  <si>
+    <t>7883C1AC0E365372A0B6DDC2141E29A2</t>
+  </si>
+  <si>
+    <t>Ley de las Entidades Paraestatales del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/10/1995</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_las_entidades_paraestatales_tlax120418.pdf</t>
+  </si>
+  <si>
+    <t>E9AB786CBC89C1EE99BDC6F51C6EA3E4</t>
+  </si>
+  <si>
+    <t>Ley Laboral de los Servidores Públicos del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>31/12/2017</t>
+  </si>
+  <si>
+    <t>22/12/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_laboral_Serv_Pub_Tlax_y_Mpios221221.pdf</t>
+  </si>
+  <si>
+    <t>19A085392E94D0E63AC6E53B07653C44</t>
+  </si>
+  <si>
+    <t>Ley de Educación para el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>29/11/2000</t>
+  </si>
+  <si>
+    <t>31/03/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_educacion_Tlax310322.pdf</t>
+  </si>
+  <si>
+    <t>6EECFA314EB7CAE697C6CF0BB51EFF93</t>
+  </si>
+  <si>
+    <t>Ley Federal</t>
+  </si>
+  <si>
+    <t>Ley Federal del Trabajo</t>
+  </si>
+  <si>
+    <t>01/05/1970</t>
+  </si>
+  <si>
+    <t>18/05/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/LeyFederalTrabajo180522.pdf</t>
+  </si>
+  <si>
+    <t>9852D248CFAB2668EF8999DD7B75585B</t>
+  </si>
+  <si>
+    <t>Ley General</t>
+  </si>
+  <si>
+    <t>Ley General para la Carrera de las Maestras y los Maestros</t>
+  </si>
+  <si>
+    <t>30/03/2019</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Gral%20del%20Sistema%20para%20la%20carrera%20de%20las%20maestras%20y%20maestros.pdf</t>
+  </si>
+  <si>
+    <t>4DD7357C1B7DB138153C3A4B0AA69AD0</t>
+  </si>
+  <si>
+    <t>Ley General de Educación</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Nueva%20Ley%20General%20de%20Educaci%C3%B3n.pdf</t>
+  </si>
+  <si>
+    <t>1852EF95D3CC5AD4EEEF778AADC741D5</t>
+  </si>
+  <si>
+    <t>Tratado internacional</t>
+  </si>
+  <si>
+    <t>Co-87- Convenio Sobre la Libertad Sindical y la Protección del Derecho de Sindicación, 1948 (núm. 87)</t>
+  </si>
+  <si>
+    <t>09/07/1948</t>
+  </si>
+  <si>
+    <t>https://www.ilo.org/dyn/normlex/es/f?p=NORMLEXPUB:12100:0::NO::P12100_ILO_CODE:C087</t>
+  </si>
+  <si>
+    <t>El Colegio de Bachilleres del Estado de Tlaxcala manifiesta a través de la Unidad Admnistrativa Subdireccióm Jurídica que este documento al ser un acuerdo celebrado y un pacto de voluntades entre varios Países a nivel internacional, no es sujeto de reforma.</t>
+  </si>
+  <si>
+    <t>96E33BA62AB36F996C02DA5D01B877D7</t>
+  </si>
+  <si>
+    <t>Co85-Convenio sobre la Inspección del Trabajo, 1947 (núm. 85)</t>
+  </si>
+  <si>
+    <t>11/07/1947</t>
+  </si>
+  <si>
+    <t>https://www.ilo.org/dyn/normlex/es/f?p=NORMLEXPUB:12100:0::NO::P12100_ILO_CODE:C085</t>
+  </si>
+  <si>
+    <t>7D20D7F8E63E1B90B9453AFA08C5EAE7</t>
+  </si>
+  <si>
+    <t>Convención Interamericana para Prevenir, Sancionar y Erradicar la Violencia contra la Mujer (Convención de Belém Do Pará)</t>
+  </si>
+  <si>
+    <t>09/06/1994</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CONVENCION%20PARA%20prevenir,sancionar%20y%20erradicar%20violenciamujer.pdf</t>
+  </si>
+  <si>
+    <t>43D1E1D6A2CD77D545A39180BDE7B1E1</t>
+  </si>
+  <si>
+    <t>Convención sobre los Derechos del Niño</t>
+  </si>
+  <si>
+    <t>20/11/1989</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Convenci%c3%b3nsobrederechosdelni%c3%b1o.pdf</t>
+  </si>
+  <si>
+    <t>2EA5FCFEF79A4CE22D622C8E0B7C9BDE</t>
+  </si>
+  <si>
+    <t>Convención Americana sobre los Derechos del Hombre (Pacto de San José)</t>
+  </si>
+  <si>
+    <t>18/07/1978</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CONVENCIONAAMERICANA%20SOBRED.H..pdf</t>
+  </si>
+  <si>
+    <t>D4856C921F24A4BF07D893F785246FDB</t>
+  </si>
+  <si>
+    <t>Constitución Política de la entidad federativa</t>
+  </si>
+  <si>
+    <t>Constitución Política del Estado Libre y Soberano de Tlaxcala</t>
+  </si>
+  <si>
+    <t>05/02/2017</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Constitucion_Pol-Tlaxcala250422pdf.pdf</t>
+  </si>
+  <si>
+    <t>402C71DDD77AC0637287B97D66E7C9EE</t>
+  </si>
+  <si>
+    <t>Constitución Política de los Estados Unidos Mexicanos</t>
+  </si>
+  <si>
+    <t>Constitución Política de los Estadod Unidos Mexicanos</t>
+  </si>
+  <si>
+    <t>28/05/2021</t>
   </si>
   <si>
     <t>Estatuto</t>
-  </si>
-  <si>
-    <t>Manual de Organizaciòn para los Servidores Pùblicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Documento admnistrativo interno en revisiòn ante la Contraloria del Ejecutivo para su validaciòn y autorizaciòn</t>
-  </si>
-  <si>
-    <t>Manual de Procedimientos de Control Interno del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Constitución Política de los Estados Unidos Mexicanos</t>
-  </si>
-  <si>
-    <t>05/02/2017</t>
-  </si>
-  <si>
-    <t>28/05/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Const.%20Fedral%2028-mayo-21.pdf</t>
-  </si>
-  <si>
-    <t>Constitución Política de la entidad federativa</t>
-  </si>
-  <si>
-    <t>Constitución Política del Estado Libre y Soberano de Tlaxcala</t>
-  </si>
-  <si>
-    <t>18/07/2017</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/CONSTITUCION-LOCAL.pdf</t>
-  </si>
-  <si>
-    <t>Ley General</t>
-  </si>
-  <si>
-    <t>Ley General de Educación</t>
-  </si>
-  <si>
-    <t>30/09/2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Nueva%20Ley%20General%20de%20Educaci%C3%B3n.pdf</t>
-  </si>
-  <si>
-    <t>Al ser una Ley de nueva creación, no existe fecha de modificación o reforma</t>
-  </si>
-  <si>
-    <t>Ley Reglamentaria</t>
-  </si>
-  <si>
-    <t>Ley Reglamentaria del Artículo 3o. de la Constitución Política de los Estados Unidos Mexicanos,  en materia de Mejora Continua de la Educación</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Reglamentaria%20del%20art.%203%20de%20la%20CPM%20en%20materia%20de%20mejora%20continua%20de%20la%20Educacion.pdf</t>
-  </si>
-  <si>
-    <t>Ley General del Sistema para la Carrera de las Maestras y los Maestros</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Gral%20del%20Sistema%20para%20la%20carrera%20de%20las%20maestras%20y%20maestros.pdf</t>
-  </si>
-  <si>
-    <t>Ley Local</t>
-  </si>
-  <si>
-    <t>Ley de Educación para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>29/11/2000</t>
-  </si>
-  <si>
-    <t>17/08/2017</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Educacion_para_el_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley Federal</t>
-  </si>
-  <si>
-    <t>Ley Federal del Trabajo</t>
-  </si>
-  <si>
-    <t>01/05/1970</t>
-  </si>
-  <si>
-    <t>02/07/2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/ley%20federal%20del%20Trab.pdf</t>
-  </si>
-  <si>
-    <t>Ley Laboral de los Servidores Públicos del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>31/12/2007</t>
-  </si>
-  <si>
-    <t>12/12/2013</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_Laboral_de_los_Servidores_Publicos_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley Orgánica</t>
-  </si>
-  <si>
-    <t>Ley Orgánica de la Administración Pública del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>07/04/1998</t>
-  </si>
-  <si>
-    <t>30/12/2015</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_Organica_de_la_Administracion_Publica_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley de las Entidades Paraestatales para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/10/1995</t>
-  </si>
-  <si>
-    <t>17/10/2008</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_las_Entidades_Paraestatales_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley del Procedimiento Administrativo del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>30/11/2001</t>
-  </si>
-  <si>
-    <t>30/11/2011</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_del_Procedimiento_Administrativo_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Transparencia y Acceso a la Información Pública para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>22/05/2012</t>
-  </si>
-  <si>
-    <t>15/11/2016</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Transparencia_y_Acceso_a_la_Informacion_Publica_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Entrega-Recepción para el Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>18/05/2011</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Entrega_Recepcion_para_el_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Protección de Datos Personales para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>14/05/2012</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/LEY_DE_DATOS.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Archivos del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/05/2011</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Archivos_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Mejora Regulatoria del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>09/05/2013</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Mejora_Regulatoria_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>05/08/1981</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_que_crea_el_Colegio_de_Bachilleres_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Reglamento General de la Ley que Crea El Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>06/02/1985</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Reglamento-General-de-la-Ley-Que-Crea-el-Colegio-de-Bachilleres-del-Estado-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>28/04/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/portal/pdf.html?p=transparencia/RICOBAT&amp;t=REGLAMENTO%20INTERIOR%20COBAT</t>
-  </si>
-  <si>
-    <t>F23D42B5A0049988</t>
-  </si>
-  <si>
-    <t>01/10/2021</t>
-  </si>
-  <si>
-    <t>31/12/2021</t>
-  </si>
-  <si>
-    <t>17/12/2021</t>
-  </si>
-  <si>
-    <t>6F9375B8A005DB5A</t>
-  </si>
-  <si>
-    <t>D33A7C2E8BDD3764</t>
-  </si>
-  <si>
-    <t>645AE057C6B09E15</t>
-  </si>
-  <si>
-    <t>11C969F450D5F06B</t>
-  </si>
-  <si>
-    <t>3C3E00B8FBE1DA85</t>
-  </si>
-  <si>
-    <t>7CF491179C2FCCB4</t>
-  </si>
-  <si>
-    <t>0F3311FD5F7F361F</t>
-  </si>
-  <si>
-    <t>4E89C46859D02C26</t>
-  </si>
-  <si>
-    <t>1716B07878A01E90</t>
-  </si>
-  <si>
-    <t>41A21DB2FCA74428</t>
-  </si>
-  <si>
-    <t>80D90C296FCE363B</t>
-  </si>
-  <si>
-    <t>3246ACC6A313E158</t>
-  </si>
-  <si>
-    <t>9BE72453CA9B8BED</t>
-  </si>
-  <si>
-    <t>A53715FC98149BB0</t>
-  </si>
-  <si>
-    <t>5551CE67C14A2E02</t>
-  </si>
-  <si>
-    <t>A6D6AADE09127019</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de octubre de 2021 al 31 de diciembre de 2021, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública de esta Ley, la cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>D9A02C9DDFDA490A</t>
-  </si>
-  <si>
-    <t>68E7DF86830DADCE</t>
-  </si>
-  <si>
-    <t>50AA6C6E0CA9C39F</t>
-  </si>
-  <si>
-    <t>C7974B7EF5822E81</t>
-  </si>
-  <si>
-    <t>012436521202181F</t>
-  </si>
-  <si>
-    <t>58F1715E7D79B54C</t>
-  </si>
-  <si>
-    <t>0517B32D9AFFCA67</t>
-  </si>
-  <si>
-    <t>61F88150BCC1D00C</t>
-  </si>
-  <si>
-    <t>C2B014D8BAE8C69F</t>
-  </si>
-  <si>
-    <t>9FC5CC193366F585</t>
-  </si>
-  <si>
-    <t>3EB920165EB0313A</t>
-  </si>
-  <si>
-    <t>Tratado internacional</t>
   </si>
   <si>
     <t>Decreto</t>
@@ -679,7 +724,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -693,9 +738,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -998,22 +1040,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="121.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="121" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="242.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="179.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="217.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -1186,1150 +1228,1314 @@
     </row>
     <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="6">
-        <v>42771</v>
+        <v>43</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>158</v>
+        <v>99</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="M28" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>60</v>
+        <v>157</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>65</v>
+        <v>161</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>69</v>
+        <v>160</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>71</v>
+      <c r="G36" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2343,7 +2549,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E145">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -2358,152 +2564,152 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
